--- a/consent_forms/020_entertainment_standards_acknowledgment--consent_forms.xlsx
+++ b/consent_forms/020_entertainment_standards_acknowledgment--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'director'}</t>
+          <t>director</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Director'}</t>
+          <t>Director</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'cast'}</t>
+          <t>cast</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Cast'}</t>
+          <t>Cast</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'crew'}</t>
+          <t>crew</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Crew'}</t>
+          <t>Crew</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'director'}</t>
+          <t>director</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Director'}</t>
+          <t>Director</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'cast'}</t>
+          <t>cast</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Cast'}</t>
+          <t>Cast</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'crew'}</t>
+          <t>crew</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Crew'}</t>
+          <t>Crew</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'john'}</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'John'}</t>
+          <t>John</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'jane'}</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Jane'}</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'bob'}</t>
+          <t>bob</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Bob'}</t>
+          <t>Bob</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'john'}</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'John'}</t>
+          <t>John</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'jane'}</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Jane'}</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'bob'}</t>
+          <t>bob</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Bob'}</t>
+          <t>Bob</t>
         </is>
       </c>
     </row>
@@ -1093,12 +1093,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'john'}</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'John'}</t>
+          <t>John</t>
         </is>
       </c>
     </row>
@@ -1110,12 +1110,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'jane'}</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Jane'}</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
@@ -1127,12 +1127,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'bob'}</t>
+          <t>bob</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Bob'}</t>
+          <t>Bob</t>
         </is>
       </c>
     </row>
